--- a/artfynd/S 739-2023 artfynd.xlsx
+++ b/artfynd/S 739-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3760,10 +3760,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>69839245</v>
+        <v>137437736</v>
       </c>
       <c r="B30" t="n">
-        <v>106229</v>
+        <v>98503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,26 +3771,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221725</v>
+        <v>220686</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3798,16 +3798,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gröne mad Naturreservat, Vg</t>
+          <t>Mösseberg, ca 50m mot Norra Grindstugan, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>412421</v>
+        <v>411899</v>
       </c>
       <c r="R30" t="n">
-        <v>6450260</v>
+        <v>6451434</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3829,22 +3832,22 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Vilske-Kleva</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Granskog, blandskog, sumpskog, vägar och diken</t>
+          <t>1 större planta i slänten ner mot östra vägdiket</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,33 +3856,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69839245</t>
+          <t>https://artportalen.se/Sighting/137437736</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>69839246</v>
+        <v>69839245</v>
       </c>
       <c r="B31" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,24 +3891,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gröne mad Naturreservat, Vg</t>
@@ -3977,13 +3990,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69839246</t>
+          <t>https://artportalen.se/Sighting/69839245</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130541598</v>
+        <v>69839246</v>
       </c>
       <c r="B32" t="n">
         <v>97983</v>
@@ -4014,14 +4027,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NV om Gröna mads naturreservat, Mösseberg, Vg</t>
+          <t>Gröne mad Naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>412037</v>
+        <v>412421</v>
       </c>
       <c r="R32" t="n">
-        <v>6451362</v>
+        <v>6450260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,27 +4056,22 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Vilske-Kleva</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Granskog, blandskog, sumpskog, vägar och diken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,44 +4086,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexander Spak</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexander Spak</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130541598</t>
+          <t>https://artportalen.se/Sighting/69839246</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>79320751</v>
+        <v>130541598</v>
       </c>
       <c r="B33" t="n">
-        <v>102560</v>
+        <v>97983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222133</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4126,14 +4134,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>S vägdiket efter S-kurvan, Mösseberg, Vg</t>
+          <t>NV om Gröna mads naturreservat, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>412474</v>
+        <v>412037</v>
       </c>
       <c r="R33" t="n">
-        <v>6450939</v>
+        <v>6451362</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4160,17 +4168,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 ex strax före mötesskylten, i blom</t>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4185,69 +4198,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Alexander Spak</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Alexander Spak</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79320751</t>
+          <t>https://artportalen.se/Sighting/130541598</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7120318</v>
+        <v>79320751</v>
       </c>
       <c r="B34" t="n">
-        <v>101326</v>
+        <v>102560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>222133</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Falköping, Vg</t>
+          <t>S vägdiket efter S-kurvan, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>412383</v>
+        <v>412474</v>
       </c>
       <c r="R34" t="n">
-        <v>6450288</v>
+        <v>6450939</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4271,17 +4280,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2011-04-21</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2011-04-21</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;29174</t>
+          <t>1 ex strax före mötesskylten, i blom</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4296,27 +4305,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7120318</t>
+          <t>https://artportalen.se/Sighting/79320751</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>69839247</v>
+        <v>7120318</v>
       </c>
       <c r="B35" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4324,37 +4333,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gröne mad Naturreservat, Vg</t>
+          <t>Falköping, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412421</v>
+        <v>412383</v>
       </c>
       <c r="R35" t="n">
-        <v>6450260</v>
+        <v>6450288</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4373,22 +4386,22 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Vilske-Kleva</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2011-04-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2011-04-21</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Granskog, blandskog, sumpskog, vägar och diken</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;29174</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4403,24 +4416,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69839247</t>
+          <t>https://artportalen.se/Sighting/7120318</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110596913</v>
+        <v>69839247</v>
       </c>
       <c r="B36" t="n">
         <v>101228</v>
@@ -4451,17 +4464,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Store Mosse Öst, Vg</t>
+          <t>Gröne mad Naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411790</v>
+        <v>412421</v>
       </c>
       <c r="R36" t="n">
-        <v>6451333</v>
+        <v>6450260</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4480,17 +4493,22 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Vilske-Kleva</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Granskog, blandskog, sumpskog, vägar och diken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4501,40 +4519,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering (NVI) av två områden på Mösseberg 2023</t>
-        </is>
-      </c>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110596913</t>
+          <t>https://artportalen.se/Sighting/69839247</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5922164</v>
+        <v>110596913</v>
       </c>
       <c r="B37" t="n">
-        <v>99036</v>
+        <v>101228</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4542,37 +4551,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>222771</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>vägkanter efter s-kurvan, Mösseberg, Vg</t>
+          <t>Store Mosse Öst, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412615</v>
+        <v>411790</v>
       </c>
       <c r="R37" t="n">
-        <v>6450831</v>
+        <v>6451333</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4596,17 +4605,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2005-07-14</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2005-07-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>åtm 15 blommande, ej bestämda till skogsnycklar/j.m.n</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,28 +4621,37 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI) av två områden på Mösseberg 2023</t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5922164</t>
+          <t>https://artportalen.se/Sighting/110596913</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>69884573</v>
+        <v>5922164</v>
       </c>
       <c r="B38" t="n">
         <v>99036</v>
@@ -4666,29 +4679,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gröne mad NR - Gröne mad norr om, Vg</t>
+          <t>vägkanter efter s-kurvan, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>412448</v>
+        <v>412615</v>
       </c>
       <c r="R38" t="n">
-        <v>6450301</v>
+        <v>6450831</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4707,22 +4711,22 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Vilske-Kleva</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2017-07-05</t>
+          <t>2005-07-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2017-07-05</t>
+          <t>2005-07-14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>skogsväg och vägdiken</t>
+          <t>åtm 15 blommande, ej bestämda till skogsnycklar/j.m.n</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4737,24 +4741,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69884573</t>
+          <t>https://artportalen.se/Sighting/5922164</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>79320753</v>
+        <v>69884573</v>
       </c>
       <c r="B39" t="n">
         <v>99036</v>
@@ -4782,20 +4786,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>S vägdiket efter S-kurvan, Mösseberg, Vg</t>
+          <t>Gröne mad NR - Gröne mad norr om, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>412474</v>
+        <v>412448</v>
       </c>
       <c r="R39" t="n">
-        <v>6450939</v>
+        <v>6450301</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4814,22 +4827,22 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Vilske-Kleva</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2017-07-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2017-07-05</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>skogsväg och vägdiken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4844,24 +4857,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79320753</t>
+          <t>https://artportalen.se/Sighting/69884573</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>79320768</v>
+        <v>79320753</v>
       </c>
       <c r="B40" t="n">
         <v>99036</v>
@@ -4892,14 +4905,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N vägdiket efter S-kurvan, Mösseberg, Vg</t>
+          <t>S vägdiket efter S-kurvan, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>412635</v>
+        <v>412474</v>
       </c>
       <c r="R40" t="n">
-        <v>6450811</v>
+        <v>6450939</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4936,7 +4949,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 ex (där det tidigare funnits massor)</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,13 +4975,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79320768</t>
+          <t>https://artportalen.se/Sighting/79320753</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>81216112</v>
+        <v>79320768</v>
       </c>
       <c r="B41" t="n">
         <v>99036</v>
@@ -4999,17 +5012,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Falköpings kommun, Vg</t>
+          <t>N vägdiket efter S-kurvan, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>412767</v>
+        <v>412635</v>
       </c>
       <c r="R41" t="n">
-        <v>6450770</v>
+        <v>6450811</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5028,22 +5041,22 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Vilske-Kleva</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2018-08-15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+          <t>2 ex (där det tidigare funnits massor)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5058,28 +5071,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Edvardsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
-        </is>
-      </c>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81216112</t>
+          <t>https://artportalen.se/Sighting/79320768</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110610641</v>
+        <v>81216112</v>
       </c>
       <c r="B42" t="n">
         <v>99036</v>
@@ -5110,14 +5119,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gröna Mad NR, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412657</v>
+        <v>412767</v>
       </c>
       <c r="R42" t="n">
-        <v>6450619</v>
+        <v>6450770</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5144,12 +5153,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2018-08-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5160,37 +5174,32 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Skogsväg och lövridå</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Erik Edvardsson, Lennart Sundh</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering (NVI) av två områden på Mösseberg 2023</t>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110610641</t>
+          <t>https://artportalen.se/Sighting/81216112</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110610644</v>
+        <v>110610641</v>
       </c>
       <c r="B43" t="n">
         <v>99036</v>
@@ -5225,13 +5234,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412680</v>
+        <v>412657</v>
       </c>
       <c r="R43" t="n">
-        <v>6450649</v>
+        <v>6450619</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5295,16 +5304,16 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110610644</t>
+          <t>https://artportalen.se/Sighting/110610641</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7119106</v>
+        <v>110610644</v>
       </c>
       <c r="B44" t="n">
-        <v>96348</v>
+        <v>99036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5312,41 +5321,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2810</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vilske-Kleva, Vg</t>
+          <t>Gröna Mad NR, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>408957</v>
+        <v>412680</v>
       </c>
       <c r="R44" t="n">
-        <v>6450313</v>
+        <v>6450649</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5365,22 +5370,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Vilske-Kleva</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2011-04-22</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2011-04-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Mille Fagerström  ID;29181</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5391,72 +5391,82 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Skogsväg och lövridå</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI) av två områden på Mösseberg 2023</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7119106</t>
+          <t>https://artportalen.se/Sighting/110610644</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16173361</v>
+        <v>7119106</v>
       </c>
       <c r="B45" t="n">
-        <v>104640</v>
+        <v>96348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220164</v>
+        <v>2810</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>hällar vid diabaskanten mitt för Lillsjön, Västerberget, Mösseberg, Vg</t>
+          <t>Vilske-Kleva, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409746</v>
+        <v>408957</v>
       </c>
       <c r="R45" t="n">
-        <v>6450067</v>
+        <v>6450313</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5475,22 +5485,22 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Gökhem</t>
+          <t>Vilske-Kleva</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2014-05-31</t>
+          <t>2011-04-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2014-05-31</t>
+          <t>2011-04-22</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>i en springa i diabasen ca 2 m nedanför kanten</t>
+          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Mille Fagerström  ID;29181</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5505,65 +5515,68 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Grahn, Jonas F Grahn</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16173361</t>
+          <t>https://artportalen.se/Sighting/7119106</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>57169157</v>
+        <v>16173361</v>
       </c>
       <c r="B46" t="n">
-        <v>100143</v>
+        <v>104640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222467</v>
+        <v>220164</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vråhålan NR - Kärr 5, Vg</t>
+          <t>hällar vid diabaskanten mitt för Lillsjön, Västerberget, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409602</v>
+        <v>409746</v>
       </c>
       <c r="R46" t="n">
-        <v>6449925</v>
+        <v>6450067</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5582,22 +5595,22 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Vilske-Kleva</t>
+          <t>Gökhem</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2015-05-23</t>
+          <t>2014-05-31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2015-05-23</t>
+          <t>2014-05-31</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Lona - Vråhålan NR - Rikkärr 5, timglaskärret, nedre.</t>
+          <t>i en springa i diabasen ca 2 m nedanför kanten</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5608,36 +5621,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Rikkärr</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Jörgen Grahn, Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57169157</t>
+          <t>https://artportalen.se/Sighting/16173361</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7120311</v>
+        <v>57169157</v>
       </c>
       <c r="B47" t="n">
-        <v>101326</v>
+        <v>100143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,41 +5653,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>222467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vilske-Kleva, Vg</t>
+          <t>Vråhålan NR - Kärr 5, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408957</v>
+        <v>409602</v>
       </c>
       <c r="R47" t="n">
-        <v>6450313</v>
+        <v>6449925</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5703,17 +5707,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2011-04-22</t>
+          <t>2015-05-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2011-04-22</t>
+          <t>2015-05-23</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;29182</t>
+          <t>Lona - Vråhålan NR - Rikkärr 5, timglaskärret, nedre.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5724,69 +5728,78 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7120311</t>
+          <t>https://artportalen.se/Sighting/57169157</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7289673</v>
+        <v>7120311</v>
       </c>
       <c r="B48" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>diabaskanten NO om Bergstugan, Västerberget, Mösseberg, Vg</t>
+          <t>Vilske-Kleva, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409667</v>
+        <v>408957</v>
       </c>
       <c r="R48" t="n">
-        <v>6449896</v>
+        <v>6450313</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,22 +5818,22 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Gökhem</t>
+          <t>Vilske-Kleva</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2014-04-26</t>
+          <t>2011-04-22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2014-04-26</t>
+          <t>2011-04-22</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>i branten, växande som de gör i stenskravel</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;29182</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5835,16 +5848,123 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120311</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7289673</v>
+      </c>
+      <c r="B49" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>diabaskanten NO om Bergstugan, Västerberget, Mösseberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>409667</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6449896</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gökhem</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2014-04-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2014-04-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>i branten, växande som de gör i stenskravel</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/7289673</t>
         </is>
@@ -5899,6 +6019,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 739-2023 artfynd.xlsx
+++ b/artfynd/S 739-2023 artfynd.xlsx
@@ -3763,7 +3763,7 @@
         <v>137437736</v>
       </c>
       <c r="B30" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 739-2023 artfynd.xlsx
+++ b/artfynd/S 739-2023 artfynd.xlsx
@@ -3763,7 +3763,7 @@
         <v>137437736</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>98507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 739-2023 artfynd.xlsx
+++ b/artfynd/S 739-2023 artfynd.xlsx
@@ -3763,7 +3763,7 @@
         <v>137437736</v>
       </c>
       <c r="B30" t="n">
-        <v>98507</v>
+        <v>98511</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
